--- a/app/data/raw/solicitudes.xlsx
+++ b/app/data/raw/solicitudes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\caba_testing\app\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD9BA596-A03A-47B8-8863-9B17B00CC55D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F3301A0-540F-4ABE-A480-E0496FA2C1B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -622,7 +622,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -652,11 +652,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
     </font>
   </fonts>
   <fills count="4">

--- a/app/data/raw/solicitudes.xlsx
+++ b/app/data/raw/solicitudes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\caba_testing\app\data\raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Norberto Luna\Desktop\caba_testing\app\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F3301A0-540F-4ABE-A480-E0496FA2C1B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDC96DA7-9AF2-4EE6-8A4B-6C9CBB49D083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -32,9 +32,9 @@
   <commentList>
     <comment ref="B2" authorId="0" shapeId="0" xr:uid="{6B154B19-8291-493F-AF29-E2A16436D4D5}">
       <text>
-        <t xml:space="preserve">[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
-Comentario:
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     Dudo de que esta consulta tenga que ser enrutada a Accesibilidad. Entiendo que apunta a algo más general. A futuro vamos a tener un agente de solicitudes que tiene que atajar este tipo de consulta. </t>
       </text>
     </comment>
@@ -1067,14 +1067,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W191"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="100.7109375" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="4.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="55.77734375" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>187</v>
       </c>
@@ -1088,7 +1089,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1100,7 +1101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -1112,7 +1113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -1124,7 +1125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -1136,7 +1137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -1148,7 +1149,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -1160,7 +1161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -1172,7 +1173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -1184,7 +1185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -1196,7 +1197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -1208,7 +1209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>11</v>
       </c>
@@ -1220,7 +1221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>12</v>
       </c>
@@ -1232,7 +1233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>13</v>
       </c>
@@ -1244,7 +1245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -1256,7 +1257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>15</v>
       </c>
@@ -1268,7 +1269,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -1280,7 +1281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -1292,7 +1293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>18</v>
       </c>
@@ -1304,7 +1305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <v>19</v>
       </c>
@@ -1316,7 +1317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>20</v>
       </c>
@@ -1328,7 +1329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
         <v>21</v>
       </c>
@@ -1340,7 +1341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>22</v>
       </c>
@@ -1352,7 +1353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="5">
         <v>23</v>
       </c>
@@ -1364,7 +1365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>24</v>
       </c>
@@ -1376,7 +1377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="5">
         <v>25</v>
       </c>
@@ -1388,7 +1389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>26</v>
       </c>
@@ -1400,7 +1401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="5">
         <v>27</v>
       </c>
@@ -1412,7 +1413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>28</v>
       </c>
@@ -1424,7 +1425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="5">
         <v>29</v>
       </c>
@@ -1436,7 +1437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>30</v>
       </c>
@@ -1448,7 +1449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="5">
         <v>31</v>
       </c>
@@ -1460,7 +1461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>32</v>
       </c>
@@ -1472,7 +1473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="5">
         <v>33</v>
       </c>
@@ -1484,7 +1485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>34</v>
       </c>
@@ -1496,7 +1497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
         <v>35</v>
       </c>
@@ -1508,7 +1509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>36</v>
       </c>
@@ -1520,7 +1521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="5">
         <v>37</v>
       </c>
@@ -1532,7 +1533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>38</v>
       </c>
@@ -1544,7 +1545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="5">
         <v>39</v>
       </c>
@@ -1556,7 +1557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>40</v>
       </c>
@@ -1568,7 +1569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="5">
         <v>41</v>
       </c>
@@ -1580,7 +1581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>42</v>
       </c>
@@ -1592,7 +1593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="5">
         <v>43</v>
       </c>
@@ -1604,7 +1605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>44</v>
       </c>
@@ -1616,7 +1617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="5">
         <v>45</v>
       </c>
@@ -1628,7 +1629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>46</v>
       </c>
@@ -1640,7 +1641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="5">
         <v>47</v>
       </c>
@@ -1652,7 +1653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>48</v>
       </c>
@@ -1664,7 +1665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="5">
         <v>49</v>
       </c>
@@ -1676,7 +1677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>50</v>
       </c>
@@ -1688,7 +1689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="5">
         <v>51</v>
       </c>
@@ -1700,7 +1701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>52</v>
       </c>
@@ -1712,7 +1713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="5">
         <v>53</v>
       </c>
@@ -1724,7 +1725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>54</v>
       </c>
@@ -1736,7 +1737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="5">
         <v>55</v>
       </c>
@@ -1748,7 +1749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>56</v>
       </c>
@@ -1760,7 +1761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="5">
         <v>57</v>
       </c>
@@ -1772,7 +1773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>58</v>
       </c>
@@ -1784,7 +1785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="5">
         <v>59</v>
       </c>
@@ -1796,7 +1797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
         <v>60</v>
       </c>
@@ -1808,7 +1809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="5">
         <v>61</v>
       </c>
@@ -1820,7 +1821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="5">
         <v>62</v>
       </c>
@@ -1832,7 +1833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="5">
         <v>63</v>
       </c>
@@ -1844,7 +1845,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
         <v>64</v>
       </c>
@@ -1856,7 +1857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="5">
         <v>65</v>
       </c>
@@ -1868,7 +1869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>66</v>
       </c>
@@ -1880,7 +1881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="5">
         <v>67</v>
       </c>
@@ -1892,7 +1893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="5">
         <v>68</v>
       </c>
@@ -1904,7 +1905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="5">
         <v>69</v>
       </c>
@@ -1916,7 +1917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="5">
         <v>70</v>
       </c>
@@ -1928,7 +1929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="5">
         <v>71</v>
       </c>
@@ -1940,7 +1941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="5">
         <v>72</v>
       </c>
@@ -1952,7 +1953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="5">
         <v>73</v>
       </c>
@@ -1964,7 +1965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="5">
         <v>74</v>
       </c>
@@ -1976,7 +1977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="5">
         <v>75</v>
       </c>
@@ -1988,7 +1989,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="5">
         <v>76</v>
       </c>
@@ -2000,7 +2001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="5">
         <v>77</v>
       </c>
@@ -2012,7 +2013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="5">
         <v>78</v>
       </c>
@@ -2024,7 +2025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="5">
         <v>79</v>
       </c>
@@ -2036,7 +2037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="5">
         <v>80</v>
       </c>
@@ -2048,7 +2049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="5">
         <v>81</v>
       </c>
@@ -2060,7 +2061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="5">
         <v>82</v>
       </c>
@@ -2072,7 +2073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="5">
         <v>83</v>
       </c>
@@ -2084,7 +2085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="5">
         <v>84</v>
       </c>
@@ -2096,7 +2097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="5">
         <v>85</v>
       </c>
@@ -2108,7 +2109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="5">
         <v>86</v>
       </c>
@@ -2120,7 +2121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="5">
         <v>87</v>
       </c>
@@ -2132,7 +2133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="5">
         <v>88</v>
       </c>
@@ -2144,7 +2145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="5">
         <v>89</v>
       </c>
@@ -2156,7 +2157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="5">
         <v>90</v>
       </c>
@@ -2168,7 +2169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="5">
         <v>91</v>
       </c>
@@ -2180,7 +2181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="5">
         <v>92</v>
       </c>
@@ -2192,7 +2193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="5">
         <v>93</v>
       </c>
@@ -2204,7 +2205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="5">
         <v>94</v>
       </c>
@@ -2216,7 +2217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="5">
         <v>95</v>
       </c>
@@ -2228,7 +2229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="5">
         <v>96</v>
       </c>
@@ -2240,7 +2241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="5">
         <v>97</v>
       </c>
@@ -2252,7 +2253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="5">
         <v>98</v>
       </c>
@@ -2264,7 +2265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="5">
         <v>99</v>
       </c>
@@ -2276,7 +2277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="5">
         <v>100</v>
       </c>
@@ -2288,7 +2289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="5">
         <v>101</v>
       </c>
@@ -2300,7 +2301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="5">
         <v>102</v>
       </c>
@@ -2312,7 +2313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="5">
         <v>103</v>
       </c>
@@ -2324,7 +2325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="5">
         <v>104</v>
       </c>
@@ -2336,7 +2337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="5">
         <v>105</v>
       </c>
@@ -2348,7 +2349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="5">
         <v>106</v>
       </c>
@@ -2360,7 +2361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="5">
         <v>107</v>
       </c>
@@ -2372,7 +2373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="5">
         <v>108</v>
       </c>
@@ -2384,7 +2385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="5">
         <v>109</v>
       </c>
@@ -2396,7 +2397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="5">
         <v>110</v>
       </c>
@@ -2408,7 +2409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" s="5">
         <v>111</v>
       </c>
@@ -2420,7 +2421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="5">
         <v>112</v>
       </c>
@@ -2432,7 +2433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="5">
         <v>113</v>
       </c>
@@ -2444,7 +2445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="5">
         <v>114</v>
       </c>
@@ -2456,7 +2457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="5">
         <v>115</v>
       </c>
@@ -2468,7 +2469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" s="5">
         <v>116</v>
       </c>
@@ -2480,7 +2481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" s="5">
         <v>117</v>
       </c>
@@ -2492,7 +2493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" s="5">
         <v>118</v>
       </c>
@@ -2504,7 +2505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="5">
         <v>119</v>
       </c>
@@ -2516,7 +2517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" s="5">
         <v>120</v>
       </c>
@@ -2528,7 +2529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" s="5">
         <v>121</v>
       </c>
@@ -2540,7 +2541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" s="5">
         <v>122</v>
       </c>
@@ -2552,7 +2553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" s="5">
         <v>123</v>
       </c>
@@ -2564,7 +2565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" s="5">
         <v>124</v>
       </c>
@@ -2576,7 +2577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" s="5">
         <v>125</v>
       </c>
@@ -2588,7 +2589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" s="5">
         <v>126</v>
       </c>
@@ -2600,7 +2601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" s="5">
         <v>127</v>
       </c>
@@ -2612,7 +2613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" s="5">
         <v>128</v>
       </c>
@@ -2624,7 +2625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" s="5">
         <v>129</v>
       </c>
@@ -2636,7 +2637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" s="5">
         <v>130</v>
       </c>
@@ -2648,7 +2649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" s="5">
         <v>131</v>
       </c>
@@ -2660,7 +2661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" s="5">
         <v>132</v>
       </c>
@@ -2672,7 +2673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" s="5">
         <v>133</v>
       </c>
@@ -2684,7 +2685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" s="5">
         <v>134</v>
       </c>
@@ -2696,7 +2697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136" s="5">
         <v>135</v>
       </c>
@@ -2708,7 +2709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137" s="5">
         <v>136</v>
       </c>
@@ -2720,7 +2721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" s="5">
         <v>137</v>
       </c>
@@ -2732,7 +2733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139" s="5">
         <v>138</v>
       </c>
@@ -2744,7 +2745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140" s="5">
         <v>139</v>
       </c>
@@ -2756,7 +2757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" s="5">
         <v>140</v>
       </c>
@@ -2768,7 +2769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142" s="5">
         <v>141</v>
       </c>
@@ -2780,7 +2781,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A143" s="5">
         <v>142</v>
       </c>
@@ -2792,7 +2793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144" s="5">
         <v>143</v>
       </c>
@@ -2804,7 +2805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145" s="5">
         <v>144</v>
       </c>
@@ -2816,7 +2817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146" s="5">
         <v>145</v>
       </c>
@@ -2828,7 +2829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147" s="5">
         <v>146</v>
       </c>
@@ -2840,7 +2841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148" s="5">
         <v>147</v>
       </c>
@@ -2852,7 +2853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149" s="5">
         <v>148</v>
       </c>
@@ -2864,7 +2865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A150" s="5">
         <v>149</v>
       </c>
@@ -2876,7 +2877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A151" s="5">
         <v>150</v>
       </c>
@@ -2888,7 +2889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A152" s="5">
         <v>151</v>
       </c>
@@ -2900,7 +2901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A153" s="5">
         <v>152</v>
       </c>
@@ -2912,7 +2913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A154" s="5">
         <v>153</v>
       </c>
@@ -2924,7 +2925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A155" s="5">
         <v>154</v>
       </c>
@@ -2936,7 +2937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A156" s="5">
         <v>155</v>
       </c>
@@ -2948,7 +2949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A157" s="5">
         <v>156</v>
       </c>
@@ -2960,7 +2961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158" s="5">
         <v>157</v>
       </c>
@@ -2972,7 +2973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A159" s="5">
         <v>158</v>
       </c>
@@ -2984,7 +2985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A160" s="5">
         <v>159</v>
       </c>
@@ -2996,7 +2997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A161" s="5">
         <v>160</v>
       </c>
@@ -3008,7 +3009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A162" s="5">
         <v>161</v>
       </c>
@@ -3020,7 +3021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A163" s="5">
         <v>162</v>
       </c>
@@ -3032,7 +3033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A164" s="5">
         <v>163</v>
       </c>
@@ -3044,7 +3045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A165" s="5">
         <v>164</v>
       </c>
@@ -3056,7 +3057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A166" s="5">
         <v>165</v>
       </c>
@@ -3068,7 +3069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A167" s="5">
         <v>166</v>
       </c>
@@ -3080,7 +3081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A168" s="5">
         <v>167</v>
       </c>
@@ -3092,7 +3093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A169" s="5">
         <v>168</v>
       </c>
@@ -3104,7 +3105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A170" s="5">
         <v>169</v>
       </c>
@@ -3116,7 +3117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A171" s="5">
         <v>170</v>
       </c>
@@ -3128,7 +3129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A172" s="5">
         <v>171</v>
       </c>
@@ -3158,7 +3159,7 @@
       <c r="V172" s="9"/>
       <c r="W172" s="9"/>
     </row>
-    <row r="173" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A173" s="6">
         <v>172</v>
       </c>
@@ -3170,7 +3171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A174" s="5">
         <v>173</v>
       </c>
@@ -3182,7 +3183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A175" s="5">
         <v>174</v>
       </c>
@@ -3194,7 +3195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A176" s="5">
         <v>175</v>
       </c>
@@ -3206,7 +3207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A177" s="5">
         <v>176</v>
       </c>
@@ -3218,7 +3219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A178" s="6">
         <v>177</v>
       </c>
@@ -3230,7 +3231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A179" s="6">
         <v>178</v>
       </c>
@@ -3242,7 +3243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A180" s="6">
         <v>179</v>
       </c>
@@ -3254,7 +3255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A181" s="6">
         <v>180</v>
       </c>
@@ -3266,7 +3267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A182" s="6">
         <v>181</v>
       </c>
@@ -3278,7 +3279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A183" s="6">
         <v>182</v>
       </c>
@@ -3290,7 +3291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A184" s="6">
         <v>183</v>
       </c>
@@ -3302,7 +3303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A185" s="5">
         <v>184</v>
       </c>
@@ -3314,7 +3315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186" s="6">
         <v>185</v>
       </c>
@@ -3326,7 +3327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A187" s="6">
         <v>186</v>
       </c>
@@ -3338,7 +3339,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A188" s="6">
         <v>187</v>
       </c>
@@ -3350,7 +3351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A189" s="11">
         <v>188</v>
       </c>
@@ -3362,7 +3363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A190" s="11">
         <v>189</v>
       </c>
@@ -3374,7 +3375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A191" s="11">
         <v>190</v>
       </c>
